--- a/results/naturverbundenheit/observables/nature-dataset-homogeneity-jensenshannon-auto.xlsx
+++ b/results/naturverbundenheit/observables/nature-dataset-homogeneity-jensenshannon-auto.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,1551 +474,1292 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03883495145631068</v>
+        <v>0.1650485436893204</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4077669902912621</v>
+        <v>0.04854368932038835</v>
       </c>
       <c r="D2" t="n">
+        <v>0.4466019417475728</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1844660194174757</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.009708737864077669</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.0970873786407767</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.1747572815533981</v>
-      </c>
       <c r="G2" t="n">
-        <v>0.2038834951456311</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.02912621359223301</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009708737864077669</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05825242718446602</v>
+        <v>0.116504854368932</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2704312685807044</v>
+        <v>0.3107425203180711</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1875</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.01041666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2272727272727273</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04545454545454546</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.01041666666666667</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.03125</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1866251840062563</v>
+        <v>0.3369025547897181</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2291666666666667</v>
+        <v>0.08421052631578947</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03125</v>
+        <v>0.2789473684210526</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1354166666666667</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.005263157894736842</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.005263157894736842</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.04210526315789474</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.04210526315789474</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01041666666666667</v>
+        <v>0.1473684210526316</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3290698290164212</v>
+        <v>0.1769939533530168</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04210526315789474</v>
+        <v>0.1714285714285714</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04210526315789474</v>
+        <v>0.1523809523809524</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2315789473684211</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1631578947368421</v>
+        <v>0.01904761904761905</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1368421052631579</v>
+        <v>0.009523809523809525</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01578947368421053</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06842105263157895</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1882080537330884</v>
+        <v>0.1294667812353465</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1523809523809524</v>
+        <v>0.2773109243697479</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1008403361344538</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02857142857142857</v>
+        <v>0.1008403361344538</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2285714285714286</v>
+        <v>0.3865546218487395</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1809523809523809</v>
+        <v>0.03361344537815126</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1238095238095238</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009523809523809525</v>
+        <v>0.008403361344537815</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.03361344537815126</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1009143981521797</v>
+        <v>0.2623851323315323</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05042016806722689</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08403361344537816</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05042016806722689</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2016806722689076</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4621848739495799</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07563025210084033</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008403361344537815</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03361344537815126</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03361344537815126</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2479177536067168</v>
+        <v>0.310779386904671</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.2232142857142857</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0625</v>
+        <v>0.08035714285714286</v>
       </c>
       <c r="D8" t="n">
-        <v>0.125</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.4821428571428572</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3125</v>
+        <v>0.02678571428571428</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3125</v>
+        <v>0.02678571428571428</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.008928571428571428</v>
       </c>
       <c r="I8" t="n">
-        <v>0.125</v>
+        <v>0.04464285714285714</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0625</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2748109372778695</v>
+        <v>0.2938786298048628</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.1379310344827586</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.06896551724137931</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06896551724137931</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.03448275862068965</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4033245847046734</v>
+        <v>0.4056239987139981</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.3391304347826087</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.1130434782608696</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.1043478260869565</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.3217391304347826</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3076923076923077</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.008695652173913044</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.02608695652173913</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="J10" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3179718199339555</v>
+        <v>0.2613967073650556</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.1852941176470588</v>
       </c>
       <c r="C11" t="n">
-        <v>0.09821428571428571</v>
+        <v>0.2970588235294118</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04464285714285714</v>
+        <v>0.1441176470588235</v>
       </c>
       <c r="E11" t="n">
-        <v>0.125</v>
+        <v>0.2117647058823529</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5267857142857143</v>
+        <v>0.04705882352941176</v>
       </c>
       <c r="G11" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.002941176470588235</v>
       </c>
       <c r="H11" t="n">
-        <v>0.008928571428571428</v>
+        <v>0.02352941176470588</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02678571428571428</v>
+        <v>0.008823529411764706</v>
       </c>
       <c r="J11" t="n">
-        <v>0.008928571428571428</v>
+        <v>0.07941176470588235</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2946901470041615</v>
+        <v>0.1931032971863478</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03448275862068965</v>
+        <v>0.1228070175438596</v>
       </c>
       <c r="E12" t="n">
-        <v>0.103448275862069</v>
+        <v>0.2280701754385965</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.03508771929824561</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03448275862068965</v>
+        <v>0.07017543859649122</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.01754385964912281</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.03508771929824561</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5044140736983753</v>
+        <v>0.1601868676333353</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03478260869565217</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2260869565217391</v>
+        <v>0.08108108108108109</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05217391304347826</v>
+        <v>0.2567567567567567</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1652173913043478</v>
+        <v>0.1486486486486487</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3304347826086956</v>
+        <v>0.01351351351351351</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05217391304347826</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01739130434782609</v>
+        <v>0.0945945945945946</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1217391304347826</v>
+        <v>0.1891891891891892</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2029285129267342</v>
+        <v>0.1973936204778306</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1823529411764706</v>
+        <v>0.1016949152542373</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1970588235294118</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="D14" t="n">
-        <v>0.005882352941176471</v>
+        <v>0.1864406779661017</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1411764705882353</v>
+        <v>0.1694915254237288</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2411764705882353</v>
+        <v>0.1016949152542373</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07352941176470588</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01764705882352941</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05</v>
+        <v>0.01694915254237288</v>
       </c>
       <c r="J14" t="n">
-        <v>0.09117647058823529</v>
+        <v>0.1525423728813559</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1301202869706584</v>
+        <v>0.1859186313553393</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.1147540983606557</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.06557377049180328</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03508771929824561</v>
+        <v>0.1967213114754098</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2456140350877193</v>
+        <v>0.2622950819672131</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.03278688524590164</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08771929824561403</v>
+        <v>0.06557377049180328</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01754385964912281</v>
+        <v>0.1639344262295082</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03508771929824561</v>
+        <v>0.08196721311475409</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2004660505684858</v>
+        <v>0.1090701885997275</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05405405405405406</v>
+        <v>0.2075471698113208</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2297297297297297</v>
+        <v>0.07547169811320754</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08108108108108109</v>
+        <v>0.119496855345912</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2972972972972973</v>
+        <v>0.5220125786163522</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1486486486486487</v>
+        <v>0.006289308176100629</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1486486486486487</v>
+        <v>0.006289308176100629</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.006289308176100629</v>
       </c>
       <c r="I16" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.01257861635220126</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01351351351351351</v>
+        <v>0.0440251572327044</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1887952228201422</v>
+        <v>0.3615835031616735</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1864406779661017</v>
+        <v>0.1162790697674419</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1864406779661017</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01694915254237288</v>
+        <v>0.1395348837209302</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1186440677966102</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2203389830508475</v>
+        <v>0.04651162790697674</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1525423728813559</v>
+        <v>0.1162790697674419</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.04651162790697674</v>
       </c>
       <c r="I17" t="n">
-        <v>0.05084745762711865</v>
+        <v>0.1162790697674419</v>
       </c>
       <c r="J17" t="n">
-        <v>0.06779661016949153</v>
+        <v>0.04651162790697674</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1341984596316853</v>
+        <v>0.05367368594948985</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.2117647058823529</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1147540983606557</v>
+        <v>0.1294117647058824</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1639344262295082</v>
+        <v>0.02352941176470588</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.2823529411764706</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2950819672131147</v>
+        <v>0.04705882352941176</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1967213114754098</v>
+        <v>0.04705882352941176</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.04705882352941176</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.1647058823529412</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.04705882352941176</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1425227024461686</v>
+        <v>0.130267926331557</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.05031446540880503</v>
+        <v>0.2178217821782178</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1886792452830189</v>
+        <v>0.1881188118811881</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.1287128712871287</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1006289308176101</v>
+        <v>0.2574257425742574</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5723270440251572</v>
+        <v>0.0396039603960396</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05660377358490566</v>
+        <v>0.04950495049504951</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01257861635220126</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.0396039603960396</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4046877245181937</v>
+        <v>0.1512606396990394</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1627906976744186</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1395348837209302</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1395348837209302</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04651162790697674</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="F20" t="n">
-        <v>0.186046511627907</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1395348837209302</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.02325581395348837</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.04651162790697674</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1162790697674419</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.06432431951867934</v>
+        <v>0.5900585746023456</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.139344262295082</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2704918032786885</v>
       </c>
       <c r="D21" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04098360655737705</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3934426229508197</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.04918032786885246</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.02459016393442623</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04098360655737705</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.02459016393442623</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2769318670268548</v>
+        <v>0.2468119628472573</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>0.143939393939394</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.07575757575757576</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.1060606060606061</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.4356060606060606</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0.0946969696969697</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.007575757575757576</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.07954545454545454</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.02651515151515152</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0.2089044370284776</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1058823529411765</v>
+        <v>0.1633466135458167</v>
       </c>
       <c r="C23" t="n">
-        <v>0.08235294117647059</v>
+        <v>0.250996015936255</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2</v>
+        <v>0.1553784860557769</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.2768924302788844</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3176470588235294</v>
+        <v>0.03386454183266932</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02352941176470588</v>
+        <v>0.00796812749003984</v>
       </c>
       <c r="H23" t="n">
-        <v>0.01176470588235294</v>
+        <v>0.02788844621513944</v>
       </c>
       <c r="I23" t="n">
-        <v>0.04705882352941176</v>
+        <v>0.01195219123505976</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03529411764705882</v>
+        <v>0.07171314741035857</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1634972150266774</v>
+        <v>0.1886851456544039</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1485148514851485</v>
+        <v>0.25</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0891089108910891</v>
+        <v>0.1225490196078431</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07920792079207921</v>
+        <v>0.2303921568627451</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1683168316831683</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3465346534653465</v>
+        <v>0.01470588235294118</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1188118811881188</v>
+        <v>0.004901960784313725</v>
       </c>
       <c r="H24" t="n">
-        <v>0.009900990099009901</v>
+        <v>0.01470588235294118</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0396039603960396</v>
+        <v>0.009803921568627451</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1838038089918234</v>
+        <v>0.2426117652995713</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.107843137254902</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.1862745098039216</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.06862745098039216</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.1274509803921569</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.009803921568627451</v>
       </c>
       <c r="J25" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.009803921568627451</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5900585746023456</v>
+        <v>0.1655630947121726</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1639344262295082</v>
+        <v>0.125</v>
       </c>
       <c r="C26" t="n">
-        <v>0.04098360655737705</v>
+        <v>0.1083333333333333</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.05</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1229508196721311</v>
+        <v>0.225</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4754098360655737</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="G26" t="n">
-        <v>0.04098360655737705</v>
+        <v>0.075</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00819672131147541</v>
+        <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.06557377049180328</v>
+        <v>0.05833333333333333</v>
       </c>
       <c r="J26" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2500828921503409</v>
+        <v>0.06650383523580361</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2598425196850394</v>
       </c>
       <c r="C27" t="n">
-        <v>0.06439393939393939</v>
+        <v>0.1653543307086614</v>
       </c>
       <c r="D27" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1653543307086614</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.1496062992125984</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.01574803149606299</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0946969696969697</v>
+        <v>0.007874015748031496</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0303030303030303</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.05681818181818182</v>
+        <v>0.07874015748031496</v>
       </c>
       <c r="J27" t="n">
-        <v>0.003787878787878788</v>
+        <v>0.1574803149606299</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2120289316483797</v>
+        <v>0.169725874633153</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1792828685258964</v>
+        <v>0.1603053435114504</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2131474103585657</v>
+        <v>0.267175572519084</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01195219123505976</v>
+        <v>0.1679389312977099</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09163346613545817</v>
+        <v>0.2290076335877863</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3127490039840637</v>
+        <v>0.03816793893129771</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07569721115537849</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.03053435114503817</v>
       </c>
       <c r="I28" t="n">
-        <v>0.05378486055776893</v>
+        <v>0.05343511450381679</v>
       </c>
       <c r="J28" t="n">
-        <v>0.06175298804780877</v>
+        <v>0.05343511450381679</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1818784525604813</v>
+        <v>0.1682611540793488</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.2</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3088235294117647</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="D29" t="n">
-        <v>0.009803921568627451</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E29" t="n">
-        <v>0.142156862745098</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2990196078431372</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.09803921568627451</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02450980392156863</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2270145478565228</v>
+        <v>0.3009544191654616</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2647058823529412</v>
+        <v>0.1875</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D30" t="n">
-        <v>0.009803921568627451</v>
+        <v>0.1041666666666667</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09803921568627451</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1862745098039216</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.05882352941176471</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.009803921568627451</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.06862745098039216</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1274509803921569</v>
+        <v>0.1875</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1341729564936071</v>
+        <v>0.2580814239481664</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1583333333333333</v>
+        <v>0.2448979591836735</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.1598639455782313</v>
       </c>
       <c r="D31" t="n">
-        <v>0.05833333333333333</v>
+        <v>0.1156462585034014</v>
       </c>
       <c r="E31" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.3639455782312925</v>
       </c>
       <c r="F31" t="n">
-        <v>0.275</v>
+        <v>0.003401360544217687</v>
       </c>
       <c r="G31" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.075</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="I31" t="n">
-        <v>0.025</v>
+        <v>0.01020408163265306</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1583333333333333</v>
+        <v>0.08163265306122448</v>
       </c>
       <c r="K31" t="n">
-        <v>0.09048085250606575</v>
+        <v>0.2695068202720895</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.04724409448818898</v>
+        <v>0.2244897959183673</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2125984251968504</v>
+        <v>0.04081632653061224</v>
       </c>
       <c r="D32" t="n">
-        <v>0.07086614173228346</v>
+        <v>0.3469387755102041</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2834645669291339</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1496062992125984</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1102362204724409</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.08163265306122448</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09448818897637795</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.03149606299212598</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1455336954356363</v>
+        <v>0.2385244594388188</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.09923664122137404</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2290076335877863</v>
+        <v>0.3787878787878788</v>
       </c>
       <c r="D33" t="n">
-        <v>0.02290076335877863</v>
+        <v>0.07575757575757576</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1603053435114504</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2137404580152672</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="G33" t="n">
-        <v>0.03816793893129771</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.01526717557251908</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1450381679389313</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.07633587786259542</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1163926484077217</v>
+        <v>0.3350551454805253</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="I34" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2634372697813064</v>
+        <v>0.260587290825307</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.2164948453608248</v>
       </c>
       <c r="C35" t="n">
-        <v>0.25</v>
+        <v>0.154639175257732</v>
       </c>
       <c r="D35" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.2371134020618557</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1134020618556701</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1875</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.02061855670103093</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0625</v>
+        <v>0.04123711340206185</v>
       </c>
       <c r="J35" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.2164948453608248</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1415860391501225</v>
+        <v>0.2031578941694613</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.06802721088435375</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1700680272108843</v>
+        <v>0.1604938271604938</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01020408163265306</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2006802721088435</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4149659863945578</v>
+        <v>0.02469135802469136</v>
       </c>
       <c r="G36" t="n">
-        <v>0.08163265306122448</v>
+        <v>0.01234567901234568</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.06172839506172839</v>
       </c>
       <c r="I36" t="n">
-        <v>0.03061224489795918</v>
+        <v>0.01234567901234568</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.1358024691358025</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2634092497400899</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0.08163265306122448</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.3673469387755102</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.04081632653061224</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.1836734693877551</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.1020408163265306</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.1836734693877551</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.04081632653061224</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.2313354366623875</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0.303030303030303</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.04545454545454546</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.04545454545454546</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.4848484848484849</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.04545454545454546</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.0303030303030303</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.04545454545454546</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.3715944435573003</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0.1764705882352941</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.1764705882352941</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.05882352941176471</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.1176470588235294</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.05882352941176471</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.1176470588235294</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.05882352941176471</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.1097007161498197</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.01666666666666667</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.2968934039267316</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0.08247422680412371</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.3092783505154639</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.06185567010309279</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.288659793814433</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.09278350515463918</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.1030927835051546</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.04123711340206185</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.02061855670103093</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.1963109181900806</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>United States of America</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.08641975308641975</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.2345679012345679</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.01234567901234568</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.1851851851851852</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.1604938271604938</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.1481481481481481</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.01234567901234568</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.08641975308641975</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.07407407407407407</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.1109504258333333</v>
+        <v>0.1435822976409761</v>
       </c>
     </row>
   </sheetData>
